--- a/manuscript_material/source_data/Source_Data_ED_Fig4.xlsx
+++ b/manuscript_material/source_data/Source_Data_ED_Fig4.xlsx
@@ -420,22 +420,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>outcome</t>
+          <t>repeatability_category</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>triplicates</t>
+          <t>replicate_sets</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>All 3 accepted</t>
+          <t>3/3 scored correct</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -472,7 +472,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Non-unanimous</t>
+          <t>Split (1–2/3)</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>All 3 rejected</t>
+          <t>0/3 scored correct</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -512,7 +512,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>All 3 accepted</t>
+          <t>3/3 scored correct</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -532,7 +532,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Non-unanimous</t>
+          <t>Split (1–2/3)</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>All 3 rejected</t>
+          <t>0/3 scored correct</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -572,7 +572,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>All 3 accepted</t>
+          <t>3/3 scored correct</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -592,7 +592,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Non-unanimous</t>
+          <t>Split (1–2/3)</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -612,7 +612,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>All 3 rejected</t>
+          <t>0/3 scored correct</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>All 3 accepted</t>
+          <t>3/3 scored correct</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -652,7 +652,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Non-unanimous</t>
+          <t>Split (1–2/3)</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -672,7 +672,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>All 3 rejected</t>
+          <t>0/3 scored correct</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>All 3 accepted</t>
+          <t>3/3 scored correct</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -712,7 +712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Non-unanimous</t>
+          <t>Split (1–2/3)</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -732,7 +732,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>All 3 rejected</t>
+          <t>0/3 scored correct</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -752,7 +752,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>All 3 accepted</t>
+          <t>3/3 scored correct</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Non-unanimous</t>
+          <t>Split (1–2/3)</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -792,7 +792,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>All 3 rejected</t>
+          <t>0/3 scored correct</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>All 3 accepted</t>
+          <t>3/3 scored correct</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Non-unanimous</t>
+          <t>Split (1–2/3)</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -852,7 +852,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>All 3 rejected</t>
+          <t>0/3 scored correct</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -872,7 +872,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>All 3 accepted</t>
+          <t>3/3 scored correct</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Non-unanimous</t>
+          <t>Split (1–2/3)</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>All 3 rejected</t>
+          <t>0/3 scored correct</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -932,7 +932,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>All 3 accepted</t>
+          <t>3/3 scored correct</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Non-unanimous</t>
+          <t>Split (1–2/3)</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -972,7 +972,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>All 3 rejected</t>
+          <t>0/3 scored correct</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>All 3 accepted</t>
+          <t>3/3 scored correct</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Non-unanimous</t>
+          <t>Split (1–2/3)</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>All 3 rejected</t>
+          <t>0/3 scored correct</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Open-ended code: prompt length versus runs with a failed shell command</t>
+          <t>Open-ended code condition: prompt length versus runs with a nonzero shell exit</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Galaxy: prompt length versus runs with a failed Galaxy job</t>
+          <t>Galaxy condition: prompt length versus runs with a Galaxy job error</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Galaxy: jobs per run versus share of jobs that failed</t>
+          <t>Galaxy condition: analysis jobs per run versus share of Galaxy job errors</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Open-ended code: prompt length versus runs with a failed shell command</t>
+          <t>Open-ended code condition: prompt length versus runs with a nonzero shell exit</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Galaxy: prompt length versus runs with a failed Galaxy job</t>
+          <t>Galaxy condition: prompt length versus runs with a Galaxy job error</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Galaxy: jobs per run versus share of jobs that failed</t>
+          <t>Galaxy condition: analysis jobs per run versus share of Galaxy job errors</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Open-ended code: prompt length versus runs with a failed shell command</t>
+          <t>Open-ended code condition: prompt length versus runs with a nonzero shell exit</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Galaxy: prompt length versus runs with a failed Galaxy job</t>
+          <t>Galaxy condition: prompt length versus runs with a Galaxy job error</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Galaxy: jobs per run versus share of jobs that failed</t>
+          <t>Galaxy condition: analysis jobs per run versus share of Galaxy job errors</t>
         </is>
       </c>
       <c r="D10" t="n">
